--- a/source/UQ/GF_UQ.xlsx
+++ b/source/UQ/GF_UQ.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234414/Desktop/TEAMS/GF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4292D68-0890-4B4E-BE3C-7DE467131CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B0080A8-35F1-47AA-86DF-9CE770432F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31540" yWindow="8440" windowWidth="26840" windowHeight="15760" firstSheet="1" activeTab="1" xr2:uid="{841F29B7-2404-C24C-AF72-52DB8E9D628B}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
-    <sheet name="growth facility list" sheetId="1" r:id="rId2"/>
+    <sheet name="growth facility" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="41">
   <si>
     <t>Template to record Growth facilities information</t>
   </si>
@@ -72,50 +72,119 @@
     <t>For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
   </si>
   <si>
+    <t>organisation</t>
+  </si>
+  <si>
+    <t>growth facility name *</t>
+  </si>
+  <si>
+    <t>growth facility description *</t>
+  </si>
+  <si>
+    <t>growth facility type *</t>
+  </si>
+  <si>
+    <t>growth facility type brand *</t>
+  </si>
+  <si>
+    <t>growth facility model *</t>
+  </si>
+  <si>
+    <t>growth facility serial number *</t>
+  </si>
+  <si>
+    <t>containment level *</t>
+  </si>
+  <si>
+    <t>quarantine details *</t>
+  </si>
+  <si>
+    <t>growth facility ontology label</t>
+  </si>
+  <si>
+    <t>growth facility ontology ID</t>
+  </si>
+  <si>
+    <t>growth facility ontology IRI</t>
+  </si>
+  <si>
     <t>UQ</t>
   </si>
   <si>
-    <t>organization</t>
-  </si>
-  <si>
-    <t>growth facility name *</t>
-  </si>
-  <si>
-    <t>growth facility description *</t>
-  </si>
-  <si>
-    <t>growth facility type *</t>
-  </si>
-  <si>
-    <t>growth facility type brand *</t>
-  </si>
-  <si>
-    <t>growth facility model *</t>
-  </si>
-  <si>
-    <t>growth facility serial number *</t>
-  </si>
-  <si>
-    <t>containment level *</t>
-  </si>
-  <si>
-    <t>quarantine *</t>
-  </si>
-  <si>
-    <t>growth facility ontology label</t>
-  </si>
-  <si>
-    <t>growth facility ontology ID</t>
-  </si>
-  <si>
-    <t>growth facility ontology IRI</t>
+    <t>Large Growth Room - 425</t>
+  </si>
+  <si>
+    <t>Large growth room in Plant Futures Facility level 4, St.Lucia Campus</t>
+  </si>
+  <si>
+    <t>walk-in growth room</t>
+  </si>
+  <si>
+    <t>PC2</t>
+  </si>
+  <si>
+    <t>Medium Growth Room 1 - 441</t>
+  </si>
+  <si>
+    <t>Medium size growth room in Plant Future Facility Level 4, St.Lucia Campus</t>
+  </si>
+  <si>
+    <t>Medium Growth Room 2 -  442</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 01 - 601</t>
+  </si>
+  <si>
+    <t>GlassHouse in Plant Future Facility Level 6, St.Lucia Campus</t>
+  </si>
+  <si>
+    <t>greenhouse</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 02 - 602</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 03 - 603</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 04 - 604</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 05 - 605</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 06 - 606</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 07 - 607</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 08 - 608</t>
+  </si>
+  <si>
+    <t>GlassHouse Bay 09 - 609</t>
+  </si>
+  <si>
+    <t>GlassHouse 8160</t>
+  </si>
+  <si>
+    <t>Walk in glasshouse at Gatton Campus</t>
+  </si>
+  <si>
+    <t>Cravo</t>
+  </si>
+  <si>
+    <t>Greenhouse at Gatton Campus</t>
+  </si>
+  <si>
+    <t>non PC2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -124,28 +193,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -194,20 +244,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
@@ -215,10 +257,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -292,49 +338,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -684,81 +724,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4035D97-689D-46F9-BBD1-5D7B529D3E32}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="134.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="134.5" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="150.1640625" style="15" customWidth="1"/>
-    <col min="2" max="16384" width="134.5" style="15"/>
+    <col min="1" max="1" width="150.125" style="10" customWidth="1"/>
+    <col min="2" max="16384" width="134.5" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" ht="26.1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" ht="44.1">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" ht="21">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:4" ht="21">
+      <c r="A4" s="6"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="1:4" ht="21">
+      <c r="A5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="8"/>
-    </row>
-    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="44.1">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="8"/>
-    </row>
-    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" ht="21">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" ht="21">
+      <c r="A8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -767,62 +807,285 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA1F6E2-D3A0-9E4D-B5B0-2E842AF351A2}">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="39.1640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr defaultColWidth="39.125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="46.5" customWidth="1"/>
+    <col min="1" max="1" width="21.625" customWidth="1"/>
+    <col min="3" max="3" width="69.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="18.75">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="D1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12" s="16" customFormat="1">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4"/>
+      <c r="B2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="16" customFormat="1">
+      <c r="A3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="15" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="15" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1125,20 +1388,11 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0799F0F2-5831-413B-8416-D11CEE4CB8CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0799F0F2-5831-413B-8416-D11CEE4CB8CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB77F825-9500-4628-8D4E-54D19151BB98}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB77F825-9500-4628-8D4E-54D19151BB98}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/source/UQ/GF_UQ.xlsx
+++ b/source/UQ/GF_UQ.xlsx
@@ -1,53 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234414/Desktop/TEAMS/GF/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B0080A8-35F1-47AA-86DF-9CE770432F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="31540" yWindow="8440" windowWidth="26840" windowHeight="15760" firstSheet="1" activeTab="1" xr2:uid="{841F29B7-2404-C24C-AF72-52DB8E9D628B}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="2" r:id="rId1"/>
-    <sheet name="growth facility" sheetId="1" r:id="rId2"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="growth facility" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>tc={29746510-4B82-B34D-A322-979FB7950618}</author>
   </authors>
   <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{29746510-4B82-B34D-A322-979FB7950618}">
+    <comment ref="C1" authorId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Add more details in here, footprint, space, quarantine, PC level.</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -57,214 +48,243 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="41">
   <si>
-    <t>Template to record Growth facilities information</t>
-  </si>
-  <si>
-    <t>This spreadsheet serves as a template for collecting information and establishing naming conventions for APPN growth facilities and types.</t>
-  </si>
-  <si>
-    <t>1. Please only fill the columns in the growth facility template indicated with an asterisk (*) and highlighted in red. </t>
-  </si>
-  <si>
-    <t>2. For every growth facility name/ID listed please add a growth facilty type, we will compared and standardise all the vocabulary once all the nodes give the information.</t>
-  </si>
-  <si>
-    <t>For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
-  </si>
-  <si>
-    <t>organisation</t>
-  </si>
-  <si>
-    <t>growth facility name *</t>
-  </si>
-  <si>
-    <t>growth facility description *</t>
-  </si>
-  <si>
-    <t>growth facility type *</t>
-  </si>
-  <si>
-    <t>growth facility type brand *</t>
-  </si>
-  <si>
-    <t>growth facility model *</t>
-  </si>
-  <si>
-    <t>growth facility serial number *</t>
-  </si>
-  <si>
-    <t>containment level *</t>
-  </si>
-  <si>
-    <t>quarantine details *</t>
-  </si>
-  <si>
-    <t>growth facility ontology label</t>
-  </si>
-  <si>
-    <t>growth facility ontology ID</t>
-  </si>
-  <si>
-    <t>growth facility ontology IRI</t>
-  </si>
-  <si>
-    <t>UQ</t>
-  </si>
-  <si>
-    <t>Large Growth Room - 425</t>
-  </si>
-  <si>
-    <t>Large growth room in Plant Futures Facility level 4, St.Lucia Campus</t>
-  </si>
-  <si>
-    <t>walk-in growth room</t>
-  </si>
-  <si>
-    <t>PC2</t>
-  </si>
-  <si>
-    <t>Medium Growth Room 1 - 441</t>
-  </si>
-  <si>
-    <t>Medium size growth room in Plant Future Facility Level 4, St.Lucia Campus</t>
-  </si>
-  <si>
-    <t>Medium Growth Room 2 -  442</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 01 - 601</t>
-  </si>
-  <si>
-    <t>GlassHouse in Plant Future Facility Level 6, St.Lucia Campus</t>
-  </si>
-  <si>
-    <t>greenhouse</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 02 - 602</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 03 - 603</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 04 - 604</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 05 - 605</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 06 - 606</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 07 - 607</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 08 - 608</t>
-  </si>
-  <si>
-    <t>GlassHouse Bay 09 - 609</t>
-  </si>
-  <si>
-    <t>GlassHouse 8160</t>
-  </si>
-  <si>
-    <t>Walk in glasshouse at Gatton Campus</t>
-  </si>
-  <si>
-    <t>Cravo</t>
-  </si>
-  <si>
-    <t>Greenhouse at Gatton Campus</t>
-  </si>
-  <si>
-    <t>non PC2</t>
+    <t xml:space="preserve">Template to record Growth facilities information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This spreadsheet serves as a template for collecting information and establishing naming conventions for APPN growth facilities and types.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Please only fill the columns in the growth facility template indicated with an asterisk (*) and highlighted in red. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. For every growth facility name/ID listed please add a growth facilty type, we will compared and standardise all the vocabulary once all the nodes give the information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">organisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility name *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility description *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility type *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility type brand *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility model *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility serial number *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">containment level *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quarantine details *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility ontology label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility ontology ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth facility ontology IRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large Growth Room - 425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large growth room in Plant Futures Facility level 4, St.Lucia Campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">walk-in growth room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium Growth Room 1 - 441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium size growth room in Plant Future Facility Level 4, St.Lucia Campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium Growth Room 2 -  442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 01 - 601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse in Plant Future Facility Level 6, St.Lucia Campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">greenhouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 02 - 602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 03 - 603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 04 - 604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 05 - 605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 06 - 606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 07 - 607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 08 - 608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse Bay 09 - 609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassHouse 8160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk in glasshouse at Gatton Campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cravo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenhouse at Gatton Campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non PC2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -276,318 +296,323 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.7999"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <color theme="2" tint="-0.1"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <color theme="2" tint="-0.1"/>
       </top>
       <bottom style="thin">
-        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <color theme="2" tint="-0.1"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0" tint="-0.15"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0" tint="-0.15"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0" tint="-0.15"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0" tint="-0.15"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0" tint="-0.15"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
+        <color theme="0" tint="-0.15"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="17">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD1D1D1"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9F2D0"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Liliana Andres Hernandez" id="{CB38393A-A056-F340-9F3B-F1B6B7AE83ED}" userId="S::a1234414@adelaide.edu.au::f5ea0ab9-0879-431c-9495-63f7ab505ec3" providerId="AD"/>
-</personList>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -595,33 +620,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -634,13 +650,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -650,15 +660,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -666,7 +674,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -674,63 +681,31 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" dT="2026-01-21T00:38:22.28" personId="{CB38393A-A056-F340-9F3B-F1B6B7AE83ED}" id="{29746510-4B82-B34D-A322-979FB7950618}">
-    <text>Add more details in here, footprint, space, quarantine, PC level.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4035D97-689D-46F9-BBD1-5D7B529D3E32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="134.5" defaultRowHeight="15.95"/>
+  <sheetFormatPr defaultColWidth="134.50390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="150.125" style="10" customWidth="1"/>
-    <col min="2" max="16384" width="134.5" style="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="150.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="134.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.1">
+    <row r="1" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -738,358 +713,373 @@
       <c r="C1" s="4"/>
       <c r="D1" s="5"/>
     </row>
-    <row r="2" spans="1:4" ht="44.1">
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="C2" s="7"/>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" ht="21">
+    <row r="3" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="8"/>
+      <c r="C3" s="7"/>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:4" ht="21">
+    <row r="4" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4" ht="21">
-      <c r="A5" s="9" t="s">
+    <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="5"/>
     </row>
-    <row r="6" spans="1:4" ht="44.1">
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:4" ht="21">
-      <c r="A7" s="9" t="s">
+    <row r="7" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:4" ht="21">
-      <c r="A8" s="9"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+    <row r="8" customFormat="false" ht="21" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA1F6E2-D3A0-9E4D-B5B0-2E842AF351A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="39.125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="39.125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21.625" customWidth="1"/>
-    <col min="3" max="3" width="69.375" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="69.37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="9" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="16" customFormat="1">
-      <c r="A2" s="16" t="s">
+    <row r="2" s="14" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="16" customFormat="1">
-      <c r="A3" s="16" t="s">
+    <row r="3" s="14" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A4" s="15" t="s">
+    <row r="4" s="16" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="15" t="s">
+    <row r="5" s="16" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" t="s">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" t="s">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="0" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
